--- a/output/yearly_total_coral_cover_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_2_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26789420788471</v>
+        <v>1.250772527922645</v>
       </c>
       <c r="C3" t="n">
-        <v>4.625933223365765</v>
+        <v>4.650094034367278</v>
       </c>
       <c r="D3" t="n">
-        <v>6.147758214051899</v>
+        <v>6.099338417278448</v>
       </c>
       <c r="E3" t="n">
-        <v>12.04158564530237</v>
+        <v>12.00020497956837</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.409937335651161</v>
+        <v>1.364980382061998</v>
       </c>
       <c r="C4" t="n">
-        <v>5.128080798911647</v>
+        <v>5.185559981946856</v>
       </c>
       <c r="D4" t="n">
-        <v>6.438619689759089</v>
+        <v>6.41662937545047</v>
       </c>
       <c r="E4" t="n">
-        <v>12.9766378243219</v>
+        <v>12.96716973945932</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.596720818762687</v>
+        <v>1.519889345760855</v>
       </c>
       <c r="C5" t="n">
-        <v>5.793656237153398</v>
+        <v>5.849533753712344</v>
       </c>
       <c r="D5" t="n">
-        <v>6.846349680406945</v>
+        <v>6.823211975398809</v>
       </c>
       <c r="E5" t="n">
-        <v>14.23672673632303</v>
+        <v>14.19263507487201</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.809832856334697</v>
+        <v>1.709507724208523</v>
       </c>
       <c r="C6" t="n">
-        <v>6.604060432502201</v>
+        <v>6.653402996814981</v>
       </c>
       <c r="D6" t="n">
-        <v>7.300307985207117</v>
+        <v>7.198201231669628</v>
       </c>
       <c r="E6" t="n">
-        <v>15.71420127404402</v>
+        <v>15.56111195269313</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.044584820314546</v>
+        <v>1.941199232370152</v>
       </c>
       <c r="C7" t="n">
-        <v>7.576541066928567</v>
+        <v>7.567706542131942</v>
       </c>
       <c r="D7" t="n">
-        <v>7.761120408272172</v>
+        <v>7.604804020572925</v>
       </c>
       <c r="E7" t="n">
-        <v>17.38224629551528</v>
+        <v>17.11370979507502</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.25757915583236</v>
+        <v>1.219429028713857</v>
       </c>
       <c r="C8" t="n">
-        <v>5.235118178323962</v>
+        <v>5.143677605653324</v>
       </c>
       <c r="D8" t="n">
-        <v>6.097908413624727</v>
+        <v>5.962658309066994</v>
       </c>
       <c r="E8" t="n">
-        <v>12.59060574778105</v>
+        <v>12.32576494343418</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.583712960097156</v>
+        <v>1.565153694062573</v>
       </c>
       <c r="C9" t="n">
-        <v>6.437208304641603</v>
+        <v>6.232935381199616</v>
       </c>
       <c r="D9" t="n">
-        <v>6.704313427529077</v>
+        <v>6.518408960803924</v>
       </c>
       <c r="E9" t="n">
-        <v>14.72523469226784</v>
+        <v>14.31649803606611</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.92674187400214</v>
+        <v>1.925281364058194</v>
       </c>
       <c r="C10" t="n">
-        <v>7.746991277995609</v>
+        <v>7.471652930615713</v>
       </c>
       <c r="D10" t="n">
-        <v>7.275550870589644</v>
+        <v>7.080104090627389</v>
       </c>
       <c r="E10" t="n">
-        <v>16.94928402258739</v>
+        <v>16.4770383853013</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.272404841832791</v>
+        <v>2.29474251303114</v>
       </c>
       <c r="C11" t="n">
-        <v>9.212630725707982</v>
+        <v>8.798426297276619</v>
       </c>
       <c r="D11" t="n">
-        <v>7.828517616724233</v>
+        <v>7.609080280797719</v>
       </c>
       <c r="E11" t="n">
-        <v>19.31355318426501</v>
+        <v>18.70224909110548</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.60983422317424</v>
+        <v>2.661153251519134</v>
       </c>
       <c r="C12" t="n">
-        <v>10.76908594919229</v>
+        <v>10.20023305367656</v>
       </c>
       <c r="D12" t="n">
-        <v>8.328522615218409</v>
+        <v>8.148663760201643</v>
       </c>
       <c r="E12" t="n">
-        <v>21.70744278758494</v>
+        <v>21.01005006539734</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.936958093450676</v>
+        <v>3.02106259762655</v>
       </c>
       <c r="C13" t="n">
-        <v>12.40707007866271</v>
+        <v>11.64229805212295</v>
       </c>
       <c r="D13" t="n">
-        <v>8.789507366103704</v>
+        <v>8.593030375363362</v>
       </c>
       <c r="E13" t="n">
-        <v>24.13353553821709</v>
+        <v>23.25639102511286</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.686377484015874</v>
+        <v>1.722103282973415</v>
       </c>
       <c r="C14" t="n">
-        <v>8.756207774177303</v>
+        <v>8.236097475421426</v>
       </c>
       <c r="D14" t="n">
-        <v>6.622663845831092</v>
+        <v>6.488576744385061</v>
       </c>
       <c r="E14" t="n">
-        <v>17.06524910402427</v>
+        <v>16.4467775027799</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.726118631083785</v>
+        <v>1.783118902792354</v>
       </c>
       <c r="C15" t="n">
-        <v>9.552552424477103</v>
+        <v>8.810370795020598</v>
       </c>
       <c r="D15" t="n">
-        <v>6.634003031815142</v>
+        <v>6.512285951442623</v>
       </c>
       <c r="E15" t="n">
-        <v>17.91267408737603</v>
+        <v>17.10577564925557</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.003374000240127</v>
+        <v>2.094224932791126</v>
       </c>
       <c r="C16" t="n">
-        <v>11.41313122113453</v>
+        <v>10.32096635259108</v>
       </c>
       <c r="D16" t="n">
-        <v>7.118377714136433</v>
+        <v>7.00718496915344</v>
       </c>
       <c r="E16" t="n">
-        <v>20.53488293551109</v>
+        <v>19.42237625453565</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.608308906574168</v>
+        <v>1.700681548066749</v>
       </c>
       <c r="C17" t="n">
-        <v>10.65017581025616</v>
+        <v>9.428155172871989</v>
       </c>
       <c r="D17" t="n">
-        <v>6.60364739279983</v>
+        <v>6.516870713221456</v>
       </c>
       <c r="E17" t="n">
-        <v>18.86213210963016</v>
+        <v>17.64570743416019</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.824057782059446</v>
+        <v>1.956358102683747</v>
       </c>
       <c r="C18" t="n">
-        <v>12.54503723674589</v>
+        <v>10.90995607027691</v>
       </c>
       <c r="D18" t="n">
-        <v>7.025396389067216</v>
+        <v>6.942693962461466</v>
       </c>
       <c r="E18" t="n">
-        <v>21.39449140787255</v>
+        <v>19.80900813542213</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.817804049183394</v>
+        <v>1.978516148368597</v>
       </c>
       <c r="C19" t="n">
-        <v>13.52721690998257</v>
+        <v>11.60636862176143</v>
       </c>
       <c r="D19" t="n">
-        <v>7.096406200515388</v>
+        <v>7.047210823055583</v>
       </c>
       <c r="E19" t="n">
-        <v>22.44142715968135</v>
+        <v>20.63209559318561</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.01615635534942</v>
+        <v>2.217041570592402</v>
       </c>
       <c r="C20" t="n">
-        <v>15.64108661433567</v>
+        <v>13.29042918119528</v>
       </c>
       <c r="D20" t="n">
-        <v>7.504862332867275</v>
+        <v>7.52389842085262</v>
       </c>
       <c r="E20" t="n">
-        <v>25.16210530255237</v>
+        <v>23.0313691726403</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.191939887726053</v>
+        <v>1.32355298495738</v>
       </c>
       <c r="C21" t="n">
-        <v>11.58999307005459</v>
+        <v>9.757865321866237</v>
       </c>
       <c r="D21" t="n">
-        <v>6.232026434311285</v>
+        <v>6.271639954177645</v>
       </c>
       <c r="E21" t="n">
-        <v>19.01395939209193</v>
+        <v>17.35305826100126</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_2_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.250772527922645</v>
+        <v>1.274560274796545</v>
       </c>
       <c r="C3" t="n">
-        <v>4.650094034367278</v>
+        <v>4.582657784562565</v>
       </c>
       <c r="D3" t="n">
-        <v>6.099338417278448</v>
+        <v>6.084926360980104</v>
       </c>
       <c r="E3" t="n">
-        <v>12.00020497956837</v>
+        <v>11.94214442033921</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.364980382061998</v>
+        <v>1.430207852918939</v>
       </c>
       <c r="C4" t="n">
-        <v>5.185559981946856</v>
+        <v>5.025479314311892</v>
       </c>
       <c r="D4" t="n">
-        <v>6.41662937545047</v>
+        <v>6.271233713494321</v>
       </c>
       <c r="E4" t="n">
-        <v>12.96716973945932</v>
+        <v>12.72692088072515</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.519889345760855</v>
+        <v>1.640760402267385</v>
       </c>
       <c r="C5" t="n">
-        <v>5.849533753712344</v>
+        <v>5.607302192549722</v>
       </c>
       <c r="D5" t="n">
-        <v>6.823211975398809</v>
+        <v>6.519834521096873</v>
       </c>
       <c r="E5" t="n">
-        <v>14.19263507487201</v>
+        <v>13.76789711591398</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.709507724208523</v>
+        <v>1.898128992001055</v>
       </c>
       <c r="C6" t="n">
-        <v>6.653402996814981</v>
+        <v>6.32406893455502</v>
       </c>
       <c r="D6" t="n">
-        <v>7.198201231669628</v>
+        <v>6.821302326023612</v>
       </c>
       <c r="E6" t="n">
-        <v>15.56111195269313</v>
+        <v>15.04350025257969</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.941199232370152</v>
+        <v>2.1937396745606</v>
       </c>
       <c r="C7" t="n">
-        <v>7.567706542131942</v>
+        <v>7.180645251790575</v>
       </c>
       <c r="D7" t="n">
-        <v>7.604804020572925</v>
+        <v>7.082657014134864</v>
       </c>
       <c r="E7" t="n">
-        <v>17.11370979507502</v>
+        <v>16.45704194048604</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.219429028713857</v>
+        <v>1.414554821556967</v>
       </c>
       <c r="C8" t="n">
-        <v>5.143677605653324</v>
+        <v>4.827250788989068</v>
       </c>
       <c r="D8" t="n">
-        <v>5.962658309066994</v>
+        <v>5.304802820239535</v>
       </c>
       <c r="E8" t="n">
-        <v>12.32576494343418</v>
+        <v>11.54660843078557</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.565153694062573</v>
+        <v>1.817933928640492</v>
       </c>
       <c r="C9" t="n">
-        <v>6.232935381199616</v>
+        <v>5.905348990713786</v>
       </c>
       <c r="D9" t="n">
-        <v>6.518408960803924</v>
+        <v>5.700710229050404</v>
       </c>
       <c r="E9" t="n">
-        <v>14.31649803606611</v>
+        <v>13.42399314840468</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.925281364058194</v>
+        <v>2.252874583995398</v>
       </c>
       <c r="C10" t="n">
-        <v>7.471652930615713</v>
+        <v>7.152975375987983</v>
       </c>
       <c r="D10" t="n">
-        <v>7.080104090627389</v>
+        <v>6.14236263868041</v>
       </c>
       <c r="E10" t="n">
-        <v>16.4770383853013</v>
+        <v>15.54821259866379</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.29474251303114</v>
+        <v>2.700908882891728</v>
       </c>
       <c r="C11" t="n">
-        <v>8.798426297276619</v>
+        <v>8.542240343322058</v>
       </c>
       <c r="D11" t="n">
-        <v>7.609080280797719</v>
+        <v>6.559536090841773</v>
       </c>
       <c r="E11" t="n">
-        <v>18.70224909110548</v>
+        <v>17.80268531705556</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.661153251519134</v>
+        <v>3.165070887737468</v>
       </c>
       <c r="C12" t="n">
-        <v>10.20023305367656</v>
+        <v>10.10343581243459</v>
       </c>
       <c r="D12" t="n">
-        <v>8.148663760201643</v>
+        <v>7.069455671099949</v>
       </c>
       <c r="E12" t="n">
-        <v>21.01005006539734</v>
+        <v>20.33796237127201</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.02106259762655</v>
+        <v>3.603027332090717</v>
       </c>
       <c r="C13" t="n">
-        <v>11.64229805212295</v>
+        <v>11.6944599162686</v>
       </c>
       <c r="D13" t="n">
-        <v>8.593030375363362</v>
+        <v>7.515802505146288</v>
       </c>
       <c r="E13" t="n">
-        <v>23.25639102511286</v>
+        <v>22.81328975350561</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.722103282973415</v>
+        <v>2.068670040049582</v>
       </c>
       <c r="C14" t="n">
-        <v>8.236097475421426</v>
+        <v>8.265589176457</v>
       </c>
       <c r="D14" t="n">
-        <v>6.488576744385061</v>
+        <v>5.752747022575035</v>
       </c>
       <c r="E14" t="n">
-        <v>16.4467775027799</v>
+        <v>16.08700623908162</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.783118902792354</v>
+        <v>2.147376753499048</v>
       </c>
       <c r="C15" t="n">
-        <v>8.810370795020598</v>
+        <v>9.01742138584625</v>
       </c>
       <c r="D15" t="n">
-        <v>6.512285951442623</v>
+        <v>5.748073903502821</v>
       </c>
       <c r="E15" t="n">
-        <v>17.10577564925557</v>
+        <v>16.91287204284812</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.094224932791126</v>
+        <v>2.515610682407942</v>
       </c>
       <c r="C16" t="n">
-        <v>10.32096635259108</v>
+        <v>10.7630669787675</v>
       </c>
       <c r="D16" t="n">
-        <v>7.00718496915344</v>
+        <v>6.195613411960771</v>
       </c>
       <c r="E16" t="n">
-        <v>19.42237625453565</v>
+        <v>19.47429107313622</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.700681548066749</v>
+        <v>2.029625933851686</v>
       </c>
       <c r="C17" t="n">
-        <v>9.428155172871989</v>
+        <v>10.03075191373868</v>
       </c>
       <c r="D17" t="n">
-        <v>6.516870713221456</v>
+        <v>5.718474210219779</v>
       </c>
       <c r="E17" t="n">
-        <v>17.64570743416019</v>
+        <v>17.77885205781015</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.956358102683747</v>
+        <v>2.329981826488955</v>
       </c>
       <c r="C18" t="n">
-        <v>10.90995607027691</v>
+        <v>11.81700259170758</v>
       </c>
       <c r="D18" t="n">
-        <v>6.942693962461466</v>
+        <v>6.088553824812657</v>
       </c>
       <c r="E18" t="n">
-        <v>19.80900813542213</v>
+        <v>20.2355382430092</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.978516148368597</v>
+        <v>2.351344656533366</v>
       </c>
       <c r="C19" t="n">
-        <v>11.60636862176143</v>
+        <v>12.76106100158836</v>
       </c>
       <c r="D19" t="n">
-        <v>7.047210823055583</v>
+        <v>6.166573314869151</v>
       </c>
       <c r="E19" t="n">
-        <v>20.63209559318561</v>
+        <v>21.27897897299088</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.217041570592402</v>
+        <v>2.630524251190032</v>
       </c>
       <c r="C20" t="n">
-        <v>13.29042918119528</v>
+        <v>14.75169191662736</v>
       </c>
       <c r="D20" t="n">
-        <v>7.52389842085262</v>
+        <v>6.555698834924416</v>
       </c>
       <c r="E20" t="n">
-        <v>23.0313691726403</v>
+        <v>23.93791500274181</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.32355298495738</v>
+        <v>1.568175060424558</v>
       </c>
       <c r="C21" t="n">
-        <v>9.757865321866237</v>
+        <v>10.89519058480504</v>
       </c>
       <c r="D21" t="n">
-        <v>6.271639954177645</v>
+        <v>5.454708054519788</v>
       </c>
       <c r="E21" t="n">
-        <v>17.35305826100126</v>
+        <v>17.91807369974939</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_2_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_2_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.274560274796545</v>
+        <v>2.597222890945509</v>
       </c>
       <c r="C3" t="n">
-        <v>4.582657784562565</v>
+        <v>7.826136438438549</v>
       </c>
       <c r="D3" t="n">
-        <v>6.084926360980104</v>
+        <v>8.187822745861032</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94214442033921</v>
+        <v>18.61118207524509</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.430207852918939</v>
+        <v>1.087106477209266</v>
       </c>
       <c r="C4" t="n">
-        <v>5.025479314311892</v>
+        <v>4.770828657657735</v>
       </c>
       <c r="D4" t="n">
-        <v>6.271233713494321</v>
+        <v>5.770407849898811</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72692088072515</v>
+        <v>11.62834298476581</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.640760402267385</v>
+        <v>1.189410641353931</v>
       </c>
       <c r="C5" t="n">
-        <v>5.607302192549722</v>
+        <v>5.69661722807402</v>
       </c>
       <c r="D5" t="n">
-        <v>6.519834521096873</v>
+        <v>6.052253845605256</v>
       </c>
       <c r="E5" t="n">
-        <v>13.76789711591398</v>
+        <v>12.93828171503321</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.898128992001055</v>
+        <v>1.29538803678923</v>
       </c>
       <c r="C6" t="n">
-        <v>6.32406893455502</v>
+        <v>6.874561241941775</v>
       </c>
       <c r="D6" t="n">
-        <v>6.821302326023612</v>
+        <v>6.388317628579478</v>
       </c>
       <c r="E6" t="n">
-        <v>15.04350025257969</v>
+        <v>14.55826690731048</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.1937396745606</v>
+        <v>1.396860387188641</v>
       </c>
       <c r="C7" t="n">
-        <v>7.180645251790575</v>
+        <v>8.232492730563884</v>
       </c>
       <c r="D7" t="n">
-        <v>7.082657014134864</v>
+        <v>6.751921845391946</v>
       </c>
       <c r="E7" t="n">
-        <v>16.45704194048604</v>
+        <v>16.38127496314447</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.414554821556967</v>
+        <v>1.497098377032139</v>
       </c>
       <c r="C8" t="n">
-        <v>4.827250788989068</v>
+        <v>9.731904815564118</v>
       </c>
       <c r="D8" t="n">
-        <v>5.304802820239535</v>
+        <v>7.107203433491607</v>
       </c>
       <c r="E8" t="n">
-        <v>11.54660843078557</v>
+        <v>18.33620662608786</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.817933928640492</v>
+        <v>1.587245582246911</v>
       </c>
       <c r="C9" t="n">
-        <v>5.905348990713786</v>
+        <v>11.36056552887044</v>
       </c>
       <c r="D9" t="n">
-        <v>5.700710229050404</v>
+        <v>7.473745370307529</v>
       </c>
       <c r="E9" t="n">
-        <v>13.42399314840468</v>
+        <v>20.42155648142488</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.252874583995398</v>
+        <v>0.9996155124641022</v>
       </c>
       <c r="C10" t="n">
-        <v>7.152975375987983</v>
+        <v>8.112142010283224</v>
       </c>
       <c r="D10" t="n">
-        <v>6.14236263868041</v>
+        <v>5.872215900704829</v>
       </c>
       <c r="E10" t="n">
-        <v>15.54821259866379</v>
+        <v>14.98397342345215</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.700908882891728</v>
+        <v>0.9170308955828607</v>
       </c>
       <c r="C11" t="n">
-        <v>8.542240343322058</v>
+        <v>8.833716755427588</v>
       </c>
       <c r="D11" t="n">
-        <v>6.559536090841773</v>
+        <v>5.703522192684099</v>
       </c>
       <c r="E11" t="n">
-        <v>17.80268531705556</v>
+        <v>15.45426984369455</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.165070887737468</v>
+        <v>0.9744042314190443</v>
       </c>
       <c r="C12" t="n">
-        <v>10.10343581243459</v>
+        <v>10.5355469483083</v>
       </c>
       <c r="D12" t="n">
-        <v>7.069455671099949</v>
+        <v>6.056971001167036</v>
       </c>
       <c r="E12" t="n">
-        <v>20.33796237127201</v>
+        <v>17.56692218089438</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.603027332090717</v>
+        <v>0.7644869372969914</v>
       </c>
       <c r="C13" t="n">
-        <v>11.6944599162686</v>
+        <v>10.02982907089669</v>
       </c>
       <c r="D13" t="n">
-        <v>7.515802505146288</v>
+        <v>5.500614577170369</v>
       </c>
       <c r="E13" t="n">
-        <v>22.81328975350561</v>
+        <v>16.29493058536405</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.068670040049582</v>
+        <v>0.8181099969029521</v>
       </c>
       <c r="C14" t="n">
-        <v>8.265589176457</v>
+        <v>11.74560989865475</v>
       </c>
       <c r="D14" t="n">
-        <v>5.752747022575035</v>
+        <v>5.797082748898821</v>
       </c>
       <c r="E14" t="n">
-        <v>16.08700623908162</v>
+        <v>18.36080264445653</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.147376753499048</v>
+        <v>0.7827179921648545</v>
       </c>
       <c r="C15" t="n">
-        <v>9.01742138584625</v>
+        <v>12.65770260328526</v>
       </c>
       <c r="D15" t="n">
-        <v>5.748073903502821</v>
+        <v>5.81410625409046</v>
       </c>
       <c r="E15" t="n">
-        <v>16.91287204284812</v>
+        <v>19.25452684954057</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.515610682407942</v>
+        <v>0.8512636168753668</v>
       </c>
       <c r="C16" t="n">
-        <v>10.7630669787675</v>
+        <v>14.74149155798024</v>
       </c>
       <c r="D16" t="n">
-        <v>6.195613411960771</v>
+        <v>6.139104014104324</v>
       </c>
       <c r="E16" t="n">
-        <v>19.47429107313622</v>
+        <v>21.73185918895993</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.029625933851686</v>
+        <v>0.5111862121242717</v>
       </c>
       <c r="C17" t="n">
-        <v>10.03075191373868</v>
+        <v>10.9774315899898</v>
       </c>
       <c r="D17" t="n">
-        <v>5.718474210219779</v>
+        <v>5.072808197567779</v>
       </c>
       <c r="E17" t="n">
-        <v>17.77885205781015</v>
+        <v>16.56142599968185</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.329981826488955</v>
+        <v>0.4042051647924969</v>
       </c>
       <c r="C18" t="n">
-        <v>11.81700259170758</v>
+        <v>9.917134251926198</v>
       </c>
       <c r="D18" t="n">
-        <v>6.088553824812657</v>
+        <v>4.564164711997506</v>
       </c>
       <c r="E18" t="n">
-        <v>20.2355382430092</v>
+        <v>14.8855041287162</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.351344656533366</v>
+        <v>0.4716512320742527</v>
       </c>
       <c r="C19" t="n">
-        <v>12.76106100158836</v>
+        <v>12.29890326981417</v>
       </c>
       <c r="D19" t="n">
-        <v>6.166573314869151</v>
+        <v>4.965709340511495</v>
       </c>
       <c r="E19" t="n">
-        <v>21.27897897299088</v>
+        <v>17.73626384239992</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.630524251190032</v>
+        <v>0.5339627588627978</v>
       </c>
       <c r="C20" t="n">
-        <v>14.75169191662736</v>
+        <v>14.86962926833853</v>
       </c>
       <c r="D20" t="n">
-        <v>6.555698834924416</v>
+        <v>5.348885469479025</v>
       </c>
       <c r="E20" t="n">
-        <v>23.93791500274181</v>
+        <v>20.75247749668035</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.568175060424558</v>
+        <v>0.5881650496142641</v>
       </c>
       <c r="C21" t="n">
-        <v>10.89519058480504</v>
+        <v>17.45263693064302</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454708054519788</v>
+        <v>5.690553305510999</v>
       </c>
       <c r="E21" t="n">
-        <v>17.91807369974939</v>
+        <v>23.73135528576828</v>
       </c>
     </row>
   </sheetData>
